--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/32.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/32.xlsx
@@ -426,13 +426,13 @@
         <v>-25.13106201901841</v>
       </c>
       <c r="E2">
-        <v>-11.57134452854121</v>
+        <v>-14.23835306756661</v>
       </c>
       <c r="F2">
-        <v>-1.518163996971412</v>
+        <v>-1.408649684484303</v>
       </c>
       <c r="G2">
-        <v>-4.938305515598231</v>
+        <v>-8.606621711298455</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-25.43608923239426</v>
       </c>
       <c r="E3">
-        <v>-11.91395075806552</v>
+        <v>-15.45879039805579</v>
       </c>
       <c r="F3">
-        <v>-1.505089874253027</v>
+        <v>-1.702692776353836</v>
       </c>
       <c r="G3">
-        <v>-5.294030254883999</v>
+        <v>-8.601218900978365</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-25.69035883998658</v>
       </c>
       <c r="E4">
-        <v>-13.49683356270662</v>
+        <v>-15.52369701600773</v>
       </c>
       <c r="F4">
-        <v>-1.341325780556579</v>
+        <v>-1.525735275033</v>
       </c>
       <c r="G4">
-        <v>-4.419678761961547</v>
+        <v>-7.685296887719285</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-25.81420611668291</v>
       </c>
       <c r="E5">
-        <v>-13.77564717888488</v>
+        <v>-17.37753653442378</v>
       </c>
       <c r="F5">
-        <v>-1.713937863846839</v>
+        <v>-1.785378753766477</v>
       </c>
       <c r="G5">
-        <v>-4.8567767106026</v>
+        <v>-8.093288519979065</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-25.76425453533039</v>
       </c>
       <c r="E6">
-        <v>-13.65707814394204</v>
+        <v>-17.50853170204366</v>
       </c>
       <c r="F6">
-        <v>-1.345526431656175</v>
+        <v>-1.740834953415739</v>
       </c>
       <c r="G6">
-        <v>-4.661570392879475</v>
+        <v>-8.149296329412456</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-25.50846995194994</v>
       </c>
       <c r="E7">
-        <v>-14.93167602356296</v>
+        <v>-17.82009524224539</v>
       </c>
       <c r="F7">
-        <v>-1.499855420634737</v>
+        <v>-1.427501669837214</v>
       </c>
       <c r="G7">
-        <v>-4.329436601106553</v>
+        <v>-7.661053762735202</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-25.02775450846296</v>
       </c>
       <c r="E8">
-        <v>-16.1941783491094</v>
+        <v>-18.97925779093678</v>
       </c>
       <c r="F8">
-        <v>-1.606274124137584</v>
+        <v>-1.353417459535244</v>
       </c>
       <c r="G8">
-        <v>-4.296582747174826</v>
+        <v>-7.318349399055387</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-24.31164360142721</v>
       </c>
       <c r="E9">
-        <v>-16.80359773869164</v>
+        <v>-19.46866809084175</v>
       </c>
       <c r="F9">
-        <v>-1.467887894193302</v>
+        <v>-1.25750991000652</v>
       </c>
       <c r="G9">
-        <v>-3.690219915656376</v>
+        <v>-6.679477010341294</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-23.38663094393289</v>
       </c>
       <c r="E10">
-        <v>-17.1552111030172</v>
+        <v>-20.08687724847288</v>
       </c>
       <c r="F10">
-        <v>-1.874440675078465</v>
+        <v>-1.343772777864449</v>
       </c>
       <c r="G10">
-        <v>-3.31804507558597</v>
+        <v>-6.745115196748425</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-22.27480541946142</v>
       </c>
       <c r="E11">
-        <v>-17.36463038350192</v>
+        <v>-20.68196854629485</v>
       </c>
       <c r="F11">
-        <v>-1.461608869280081</v>
+        <v>-1.763933978442803</v>
       </c>
       <c r="G11">
-        <v>-2.656194190283796</v>
+        <v>-6.619715042266371</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-21.05093867492407</v>
       </c>
       <c r="E12">
-        <v>-19.48199086137232</v>
+        <v>-21.92679623778934</v>
       </c>
       <c r="F12">
-        <v>-1.286459693999557</v>
+        <v>-1.485267042304035</v>
       </c>
       <c r="G12">
-        <v>-2.796610979331983</v>
+        <v>-5.96484609750652</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-19.75982083993417</v>
       </c>
       <c r="E13">
-        <v>-19.74126411220747</v>
+        <v>-21.11942366390981</v>
       </c>
       <c r="F13">
-        <v>-1.071333507859928</v>
+        <v>-1.219548317038427</v>
       </c>
       <c r="G13">
-        <v>-2.503776673655751</v>
+        <v>-5.398772605201001</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-18.50366756630526</v>
       </c>
       <c r="E14">
-        <v>-21.04497555122371</v>
+        <v>-23.09494327891196</v>
       </c>
       <c r="F14">
-        <v>-1.158485213941061</v>
+        <v>-1.14088489173378</v>
       </c>
       <c r="G14">
-        <v>-2.444613914323435</v>
+        <v>-5.37538029042051</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-17.33748315263862</v>
       </c>
       <c r="E15">
-        <v>-21.61456701190849</v>
+        <v>-23.46333011096193</v>
       </c>
       <c r="F15">
-        <v>-0.8202205566404802</v>
+        <v>-0.9957847439898074</v>
       </c>
       <c r="G15">
-        <v>-1.852254690436102</v>
+        <v>-4.597799354156494</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-16.35231008937535</v>
       </c>
       <c r="E16">
-        <v>-22.57409631244574</v>
+        <v>-24.6110220349919</v>
       </c>
       <c r="F16">
-        <v>-0.5897836557949082</v>
+        <v>-0.5075739896388768</v>
       </c>
       <c r="G16">
-        <v>-1.653562368260124</v>
+        <v>-3.831904643646105</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-15.58674196754392</v>
       </c>
       <c r="E17">
-        <v>-23.25522861641345</v>
+        <v>-24.331828026997</v>
       </c>
       <c r="F17">
-        <v>-0.05093397374344096</v>
+        <v>-0.2629049084458064</v>
       </c>
       <c r="G17">
-        <v>-1.584027669753272</v>
+        <v>-4.262391432845233</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-15.0842949679476</v>
       </c>
       <c r="E18">
-        <v>-24.43002345737932</v>
+        <v>-26.31209348275918</v>
       </c>
       <c r="F18">
-        <v>0.3748584684391441</v>
+        <v>0.05557999201072788</v>
       </c>
       <c r="G18">
-        <v>-1.179200919029034</v>
+        <v>-4.144416832007765</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-14.84816849695955</v>
       </c>
       <c r="E19">
-        <v>-25.90857927783171</v>
+        <v>-26.66928139858819</v>
       </c>
       <c r="F19">
-        <v>0.6191398736877043</v>
+        <v>0.1996405386641871</v>
       </c>
       <c r="G19">
-        <v>-1.796644146467425</v>
+        <v>-4.22329720057198</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-14.86359189653651</v>
       </c>
       <c r="E20">
-        <v>-26.04216473258398</v>
+        <v>-26.54891908793832</v>
       </c>
       <c r="F20">
-        <v>1.129105212770956</v>
+        <v>0.5391402917623421</v>
       </c>
       <c r="G20">
-        <v>-1.422535947802084</v>
+        <v>-3.607131843711748</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-15.10328460108405</v>
       </c>
       <c r="E21">
-        <v>-26.7834080005295</v>
+        <v>-27.44815175706345</v>
       </c>
       <c r="F21">
-        <v>1.382708236403219</v>
+        <v>0.7065848218294285</v>
       </c>
       <c r="G21">
-        <v>-1.589198741885614</v>
+        <v>-4.512566048702418</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-15.50929703833499</v>
       </c>
       <c r="E22">
-        <v>-27.47259645975685</v>
+        <v>-28.4044884834253</v>
       </c>
       <c r="F22">
-        <v>1.694818849695211</v>
+        <v>1.201111877626705</v>
       </c>
       <c r="G22">
-        <v>-2.26616888866564</v>
+        <v>-4.439813499931394</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-16.03838100966967</v>
       </c>
       <c r="E23">
-        <v>-27.65716347488748</v>
+        <v>-28.56053969772962</v>
       </c>
       <c r="F23">
-        <v>1.48327535257269</v>
+        <v>1.36307592895687</v>
       </c>
       <c r="G23">
-        <v>-2.188976898326453</v>
+        <v>-4.860030976867704</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-16.60788017851597</v>
       </c>
       <c r="E24">
-        <v>-28.18201361237647</v>
+        <v>-29.42981198282</v>
       </c>
       <c r="F24">
-        <v>1.876741585228427</v>
+        <v>1.300570638211231</v>
       </c>
       <c r="G24">
-        <v>-2.387344787039583</v>
+        <v>-4.725609585791136</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-17.17475835852717</v>
       </c>
       <c r="E25">
-        <v>-27.89405700717673</v>
+        <v>-29.35167316381764</v>
       </c>
       <c r="F25">
-        <v>2.100284812547902</v>
+        <v>1.580340131363125</v>
       </c>
       <c r="G25">
-        <v>-2.50813997267651</v>
+        <v>-4.759046095737776</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-17.66227508327813</v>
       </c>
       <c r="E26">
-        <v>-28.47255144776058</v>
+        <v>-29.43744246152292</v>
       </c>
       <c r="F26">
-        <v>2.058733903623478</v>
+        <v>1.71632161073708</v>
       </c>
       <c r="G26">
-        <v>-3.195786628820685</v>
+        <v>-5.005380478769405</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-18.04237654232731</v>
       </c>
       <c r="E27">
-        <v>-28.9230259281476</v>
+        <v>-28.7583660847547</v>
       </c>
       <c r="F27">
-        <v>2.249977429172995</v>
+        <v>1.707204599101869</v>
       </c>
       <c r="G27">
-        <v>-2.775615499521925</v>
+        <v>-4.519127549961254</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-18.2705995187376</v>
       </c>
       <c r="E28">
-        <v>-28.83839327741825</v>
+        <v>-29.26518383874515</v>
       </c>
       <c r="F28">
-        <v>2.111290501861496</v>
+        <v>1.473334943739096</v>
       </c>
       <c r="G28">
-        <v>-3.13884855609076</v>
+        <v>-5.020546087884806</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-18.34379256360838</v>
       </c>
       <c r="E29">
-        <v>-28.36885392145894</v>
+        <v>-29.53276683938438</v>
       </c>
       <c r="F29">
-        <v>1.753222065062187</v>
+        <v>1.766545526368814</v>
       </c>
       <c r="G29">
-        <v>-2.398550983690016</v>
+        <v>-5.041647505152121</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-18.25801700469549</v>
       </c>
       <c r="E30">
-        <v>-28.46513833581003</v>
+        <v>-28.06988406747254</v>
       </c>
       <c r="F30">
-        <v>2.013284697701481</v>
+        <v>1.560174355309373</v>
       </c>
       <c r="G30">
-        <v>-2.697572698979147</v>
+        <v>-4.909805029050646</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-18.03143754899465</v>
       </c>
       <c r="E31">
-        <v>-28.48658066023635</v>
+        <v>-29.29417060086825</v>
       </c>
       <c r="F31">
-        <v>2.069958281931412</v>
+        <v>1.571368912390806</v>
       </c>
       <c r="G31">
-        <v>-2.499194878629399</v>
+        <v>-5.455541840108423</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-17.69210276128326</v>
       </c>
       <c r="E32">
-        <v>-26.81454125933223</v>
+        <v>-28.62099482573202</v>
       </c>
       <c r="F32">
-        <v>1.837341118081671</v>
+        <v>1.337414763552947</v>
       </c>
       <c r="G32">
-        <v>-2.474825952914824</v>
+        <v>-4.767233074856393</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-17.26557486206185</v>
       </c>
       <c r="E33">
-        <v>-27.25170655461071</v>
+        <v>-28.5741070058566</v>
       </c>
       <c r="F33">
-        <v>1.774131715043652</v>
+        <v>1.337356777834751</v>
       </c>
       <c r="G33">
-        <v>-2.06407663622083</v>
+        <v>-4.973509856862841</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-16.7956021755134</v>
       </c>
       <c r="E34">
-        <v>-26.85270270979487</v>
+        <v>-27.98541897028148</v>
       </c>
       <c r="F34">
-        <v>1.79932071102798</v>
+        <v>1.284463862431197</v>
       </c>
       <c r="G34">
-        <v>-1.689491718997834</v>
+        <v>-4.887548231390126</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-16.30119250131604</v>
       </c>
       <c r="E35">
-        <v>-26.67572541710111</v>
+        <v>-27.599026925577</v>
       </c>
       <c r="F35">
-        <v>1.784996581898771</v>
+        <v>1.063496857734429</v>
       </c>
       <c r="G35">
-        <v>-1.657703860729753</v>
+        <v>-5.071048460086389</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-15.83158825978432</v>
       </c>
       <c r="E36">
-        <v>-26.75268230438746</v>
+        <v>-27.8210715915951</v>
       </c>
       <c r="F36">
-        <v>1.671853191819997</v>
+        <v>1.168719398707634</v>
       </c>
       <c r="G36">
-        <v>-1.658928762579283</v>
+        <v>-4.477848357632081</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-15.39777578671472</v>
       </c>
       <c r="E37">
-        <v>-25.47653568665591</v>
+        <v>-27.43716115064683</v>
       </c>
       <c r="F37">
-        <v>1.49161369884927</v>
+        <v>1.172297945887727</v>
       </c>
       <c r="G37">
-        <v>-0.4983971605145326</v>
+        <v>-4.12477205477773</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-15.03846416599706</v>
       </c>
       <c r="E38">
-        <v>-26.00954160583272</v>
+        <v>-27.11479719993681</v>
       </c>
       <c r="F38">
-        <v>1.240866886021859</v>
+        <v>1.375030927314073</v>
       </c>
       <c r="G38">
-        <v>-0.347992455574364</v>
+        <v>-4.071766910148459</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-14.7535623278564</v>
       </c>
       <c r="E39">
-        <v>-25.02931717908041</v>
+        <v>-26.54670013567456</v>
       </c>
       <c r="F39">
-        <v>1.400655644552273</v>
+        <v>1.068536645013061</v>
       </c>
       <c r="G39">
-        <v>-0.04518678673384634</v>
+        <v>-4.210429110060833</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-14.56047643316419</v>
       </c>
       <c r="E40">
-        <v>-24.5704016231431</v>
+        <v>-26.39204369136461</v>
       </c>
       <c r="F40">
-        <v>1.673107340067836</v>
+        <v>1.006076086107173</v>
       </c>
       <c r="G40">
-        <v>-0.7092060793642432</v>
+        <v>-4.099936342142118</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-14.45084494576569</v>
       </c>
       <c r="E41">
-        <v>-24.58856533238786</v>
+        <v>-25.78386057518646</v>
       </c>
       <c r="F41">
-        <v>1.542957567209589</v>
+        <v>0.9424524993677542</v>
       </c>
       <c r="G41">
-        <v>-0.1327937533395798</v>
+        <v>-3.25858436715512</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-14.41717379533892</v>
       </c>
       <c r="E42">
-        <v>-23.64910170017859</v>
+        <v>-25.71484210283556</v>
       </c>
       <c r="F42">
-        <v>0.9991327105369076</v>
+        <v>0.7597013964317384</v>
       </c>
       <c r="G42">
-        <v>0.2708080955351277</v>
+        <v>-3.814176672283307</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-14.44628306270838</v>
       </c>
       <c r="E43">
-        <v>-23.5990439484978</v>
+        <v>-24.65720794139613</v>
       </c>
       <c r="F43">
-        <v>0.8185469599918097</v>
+        <v>0.6128550502026645</v>
       </c>
       <c r="G43">
-        <v>-0.07987137234879058</v>
+        <v>-3.896301375476008</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-14.51225154777029</v>
       </c>
       <c r="E44">
-        <v>-24.29875205284497</v>
+        <v>-24.66002012375489</v>
       </c>
       <c r="F44">
-        <v>1.12481592635926</v>
+        <v>0.5543184676838374</v>
       </c>
       <c r="G44">
-        <v>0.08897638179065778</v>
+        <v>-3.26367267564898</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-14.60247117658559</v>
       </c>
       <c r="E45">
-        <v>-22.24247616086404</v>
+        <v>-23.83994518028384</v>
       </c>
       <c r="F45">
-        <v>1.114572335056241</v>
+        <v>0.4843785794980723</v>
       </c>
       <c r="G45">
-        <v>-0.22600216299776</v>
+        <v>-3.754216071476028</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-14.68027164830902</v>
       </c>
       <c r="E46">
-        <v>-22.09256102884012</v>
+        <v>-23.42411805452952</v>
       </c>
       <c r="F46">
-        <v>1.134764618866882</v>
+        <v>0.5964475770554146</v>
       </c>
       <c r="G46">
-        <v>0.4036933934814732</v>
+        <v>-3.264871093134196</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-14.74111281441434</v>
       </c>
       <c r="E47">
-        <v>-21.47755350233241</v>
+        <v>-22.42361964964487</v>
       </c>
       <c r="F47">
-        <v>0.8829939439296113</v>
+        <v>0.5686848435505892</v>
       </c>
       <c r="G47">
-        <v>0.2780846746304458</v>
+        <v>-3.993475818690235</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-14.7542735910306</v>
       </c>
       <c r="E48">
-        <v>-21.03999875828928</v>
+        <v>-22.18354712860223</v>
       </c>
       <c r="F48">
-        <v>1.142716945933757</v>
+        <v>0.7091676713913574</v>
       </c>
       <c r="G48">
-        <v>0.8664116540509462</v>
+        <v>-3.869598515156246</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-14.72752450450327</v>
       </c>
       <c r="E49">
-        <v>-20.82110591018052</v>
+        <v>-21.10118297060691</v>
       </c>
       <c r="F49">
-        <v>1.028826368457659</v>
+        <v>0.2981632440835491</v>
       </c>
       <c r="G49">
-        <v>0.0398545070789519</v>
+        <v>-3.761595277483063</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-14.64623860568867</v>
       </c>
       <c r="E50">
-        <v>-20.65428598468596</v>
+        <v>-22.19950094253125</v>
       </c>
       <c r="F50">
-        <v>0.8635720418035741</v>
+        <v>0.727517666098172</v>
       </c>
       <c r="G50">
-        <v>-0.1713384350533142</v>
+        <v>-3.018440704281928</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-14.52708437121776</v>
       </c>
       <c r="E51">
-        <v>-20.24053742850115</v>
+        <v>-21.64844905443388</v>
       </c>
       <c r="F51">
-        <v>1.028650754568265</v>
+        <v>0.5951544955396446</v>
       </c>
       <c r="G51">
-        <v>0.2885162036246893</v>
+        <v>-3.575903467639803</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-14.37383077083325</v>
       </c>
       <c r="E52">
-        <v>-18.92104878604219</v>
+        <v>-21.16882478685948</v>
       </c>
       <c r="F52">
-        <v>0.7719529503191431</v>
+        <v>0.3723410599020364</v>
       </c>
       <c r="G52">
-        <v>-0.05766092232582018</v>
+        <v>-4.309543532961073</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-14.20562854305716</v>
       </c>
       <c r="E53">
-        <v>-19.50011834282502</v>
+        <v>-20.39825059276628</v>
       </c>
       <c r="F53">
-        <v>0.9084811521789464</v>
+        <v>0.8901692623726606</v>
       </c>
       <c r="G53">
-        <v>0.01969659529032965</v>
+        <v>-4.182302715159185</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-14.04011176339764</v>
       </c>
       <c r="E54">
-        <v>-18.84357112424496</v>
+        <v>-20.42361457568324</v>
       </c>
       <c r="F54">
-        <v>0.9630970717803234</v>
+        <v>0.6346576802443474</v>
       </c>
       <c r="G54">
-        <v>-0.6382445357299653</v>
+        <v>-3.919339461883796</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-13.89082058143809</v>
       </c>
       <c r="E55">
-        <v>-18.42909801221892</v>
+        <v>-19.21731514104601</v>
       </c>
       <c r="F55">
-        <v>1.089780955425258</v>
+        <v>0.7158062077573927</v>
       </c>
       <c r="G55">
-        <v>-0.4953978062559529</v>
+        <v>-4.194866235480719</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-13.78071227305881</v>
       </c>
       <c r="E56">
-        <v>-17.8709364199295</v>
+        <v>-20.37304510643959</v>
       </c>
       <c r="F56">
-        <v>1.283315745210917</v>
+        <v>0.7695987301603869</v>
       </c>
       <c r="G56">
-        <v>-0.4868003194904656</v>
+        <v>-3.8866147192281</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-13.71015265538235</v>
       </c>
       <c r="E57">
-        <v>-18.25146409079404</v>
+        <v>-18.80361639807528</v>
       </c>
       <c r="F57">
-        <v>1.116283742110425</v>
+        <v>0.1501157651204159</v>
       </c>
       <c r="G57">
-        <v>-0.4993803925396961</v>
+        <v>-4.214408385799037</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-13.70220932471166</v>
       </c>
       <c r="E58">
-        <v>-17.24681760371837</v>
+        <v>-19.31433769666035</v>
       </c>
       <c r="F58">
-        <v>1.138046610516773</v>
+        <v>0.6427963899768526</v>
       </c>
       <c r="G58">
-        <v>-0.7572023685925969</v>
+        <v>-5.028090821168806</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-13.74585477857002</v>
       </c>
       <c r="E59">
-        <v>-17.50302054917632</v>
+        <v>-19.40874279429825</v>
       </c>
       <c r="F59">
-        <v>1.350668641997739</v>
+        <v>1.011916076296909</v>
       </c>
       <c r="G59">
-        <v>-1.343119270860508</v>
+        <v>-4.340384575204923</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-13.85853332514216</v>
       </c>
       <c r="E60">
-        <v>-16.14832302130773</v>
+        <v>-18.17910360462548</v>
       </c>
       <c r="F60">
-        <v>1.275883632873</v>
+        <v>0.7924434463947917</v>
       </c>
       <c r="G60">
-        <v>-1.397961768264074</v>
+        <v>-4.676120240524572</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-14.01919174229949</v>
       </c>
       <c r="E61">
-        <v>-16.47781931857983</v>
+        <v>-18.89783582827887</v>
       </c>
       <c r="F61">
-        <v>1.468402844222827</v>
+        <v>0.8413386607124353</v>
       </c>
       <c r="G61">
-        <v>-2.071383010226001</v>
+        <v>-5.071644358283457</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-14.23026592094193</v>
       </c>
       <c r="E62">
-        <v>-15.720454683167</v>
+        <v>-18.49528618831503</v>
       </c>
       <c r="F62">
-        <v>1.347673265469216</v>
+        <v>1.083319689683421</v>
       </c>
       <c r="G62">
-        <v>-2.014054293122443</v>
+        <v>-4.997441790566233</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-14.46777455596632</v>
       </c>
       <c r="E63">
-        <v>-15.87477149192638</v>
+        <v>-17.660462005001</v>
       </c>
       <c r="F63">
-        <v>1.259765259949327</v>
+        <v>0.8170509284623538</v>
       </c>
       <c r="G63">
-        <v>-1.700750884376896</v>
+        <v>-5.006052519513878</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-14.72014040851858</v>
       </c>
       <c r="E64">
-        <v>-15.71350347556523</v>
+        <v>-17.40151480429439</v>
       </c>
       <c r="F64">
-        <v>1.387953458797745</v>
+        <v>0.8042493386194902</v>
       </c>
       <c r="G64">
-        <v>-2.05717083822591</v>
+        <v>-5.590069168642247</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-14.96853172222739</v>
       </c>
       <c r="E65">
-        <v>-15.11682721184057</v>
+        <v>-17.568950602254</v>
       </c>
       <c r="F65">
-        <v>1.424037142863692</v>
+        <v>0.8346454520978153</v>
       </c>
       <c r="G65">
-        <v>-2.800494249249549</v>
+        <v>-6.103948599975617</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-15.19469694260851</v>
       </c>
       <c r="E66">
-        <v>-14.28801684200873</v>
+        <v>-17.57795320858125</v>
       </c>
       <c r="F66">
-        <v>1.288874090483702</v>
+        <v>0.5596597806970887</v>
       </c>
       <c r="G66">
-        <v>-2.286389700819508</v>
+        <v>-5.663967166169858</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-15.39238487408547</v>
       </c>
       <c r="E67">
-        <v>-14.84853776925614</v>
+        <v>-16.99368496363761</v>
       </c>
       <c r="F67">
-        <v>1.059631695432967</v>
+        <v>0.8081923674568159</v>
       </c>
       <c r="G67">
-        <v>-2.942281604150994</v>
+        <v>-5.730135039863272</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-15.54280433306614</v>
       </c>
       <c r="E68">
-        <v>-14.68239711486273</v>
+        <v>-16.75222220107462</v>
       </c>
       <c r="F68">
-        <v>0.9904431364815407</v>
+        <v>0.7777780298956293</v>
       </c>
       <c r="G68">
-        <v>-3.055664478325493</v>
+        <v>-5.621251197076642</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-15.65474465419143</v>
       </c>
       <c r="E69">
-        <v>-14.63457642934173</v>
+        <v>-16.89643598432289</v>
       </c>
       <c r="F69">
-        <v>1.232372806673553</v>
+        <v>0.7861047790285699</v>
       </c>
       <c r="G69">
-        <v>-3.011372689555584</v>
+        <v>-5.706266006525126</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-15.71290489997358</v>
       </c>
       <c r="E70">
-        <v>-15.2376378414172</v>
+        <v>-16.75810468881058</v>
       </c>
       <c r="F70">
-        <v>0.894828000646005</v>
+        <v>0.4871983421372019</v>
       </c>
       <c r="G70">
-        <v>-2.832705857346657</v>
+        <v>-5.833281707230344</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-15.73671651825892</v>
       </c>
       <c r="E71">
-        <v>-14.22041125354822</v>
+        <v>-17.05076185003028</v>
       </c>
       <c r="F71">
-        <v>0.7997860950532065</v>
+        <v>0.5136298892257285</v>
       </c>
       <c r="G71">
-        <v>-3.609313493222128</v>
+        <v>-5.918812961782954</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-15.71682566538128</v>
       </c>
       <c r="E72">
-        <v>-14.42064678874538</v>
+        <v>-16.84416833732636</v>
       </c>
       <c r="F72">
-        <v>0.775725335471492</v>
+        <v>0.3175660937593219</v>
       </c>
       <c r="G72">
-        <v>-2.626498596796533</v>
+        <v>-5.399120212482623</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-15.67407876462586</v>
       </c>
       <c r="E73">
-        <v>-14.83178241542776</v>
+        <v>-17.2309588877435</v>
       </c>
       <c r="F73">
-        <v>0.8365556673286709</v>
+        <v>0.2493094481360454</v>
       </c>
       <c r="G73">
-        <v>-3.32626847070552</v>
+        <v>-5.19800126042636</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-15.60698801241888</v>
       </c>
       <c r="E74">
-        <v>-14.47427750641822</v>
+        <v>-17.25643608251066</v>
       </c>
       <c r="F74">
-        <v>0.7415303290839285</v>
+        <v>0.2120254597034425</v>
       </c>
       <c r="G74">
-        <v>-2.634784892281329</v>
+        <v>-5.646649702453931</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-15.52829711728542</v>
       </c>
       <c r="E75">
-        <v>-14.66125819819493</v>
+        <v>-17.35367600487736</v>
       </c>
       <c r="F75">
-        <v>0.7943851395869538</v>
+        <v>0.2056163811079827</v>
       </c>
       <c r="G75">
-        <v>-3.545512659589293</v>
+        <v>-5.996544571045042</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-15.4420444175351</v>
       </c>
       <c r="E76">
-        <v>-15.7789580388721</v>
+        <v>-17.30217366998813</v>
       </c>
       <c r="F76">
-        <v>0.3053683837530992</v>
+        <v>0.2348527802223885</v>
       </c>
       <c r="G76">
-        <v>-2.978757194902684</v>
+        <v>-5.188394057271395</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-15.34914772250185</v>
       </c>
       <c r="E77">
-        <v>-15.54139429242971</v>
+        <v>-17.65841966322354</v>
       </c>
       <c r="F77">
-        <v>0.4775346080161428</v>
+        <v>0.03975900298466012</v>
       </c>
       <c r="G77">
-        <v>-2.573453725620791</v>
+        <v>-5.384259173556836</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-15.25722077282169</v>
       </c>
       <c r="E78">
-        <v>-14.68694370276643</v>
+        <v>-17.81663095962952</v>
       </c>
       <c r="F78">
-        <v>0.3989970945567217</v>
+        <v>-0.1757341499144089</v>
       </c>
       <c r="G78">
-        <v>-2.569312233151163</v>
+        <v>-5.474319254407169</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-15.15586901141989</v>
       </c>
       <c r="E79">
-        <v>-15.38140783421272</v>
+        <v>-18.20642841678776</v>
       </c>
       <c r="F79">
-        <v>0.4480091086781601</v>
+        <v>-0.03200660695687505</v>
       </c>
       <c r="G79">
-        <v>-2.06366612857396</v>
+        <v>-4.937620232671603</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-15.0576905499181</v>
       </c>
       <c r="E80">
-        <v>-16.20063142457033</v>
+        <v>-18.27008517591358</v>
       </c>
       <c r="F80">
-        <v>0.2010429646771267</v>
+        <v>-0.3873248639788894</v>
       </c>
       <c r="G80">
-        <v>-2.170000851295351</v>
+        <v>-5.329870220892149</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-14.94554240408198</v>
       </c>
       <c r="E81">
-        <v>-17.23251668280214</v>
+        <v>-19.19430143613902</v>
       </c>
       <c r="F81">
-        <v>-0.09494679058898428</v>
+        <v>-0.2568164080352301</v>
       </c>
       <c r="G81">
-        <v>-2.182385602157765</v>
+        <v>-4.706908314039794</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-14.83343946284205</v>
       </c>
       <c r="E82">
-        <v>-18.08692651619935</v>
+        <v>-19.9388821894282</v>
       </c>
       <c r="F82">
-        <v>0.1427267278874443</v>
+        <v>-0.2345482355131738</v>
       </c>
       <c r="G82">
-        <v>-1.841763571622152</v>
+        <v>-4.848288471839909</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-14.70342595645299</v>
       </c>
       <c r="E83">
-        <v>-18.00301389283722</v>
+        <v>-20.17777730722884</v>
       </c>
       <c r="F83">
-        <v>-0.4865491965884226</v>
+        <v>-0.3384337914982598</v>
       </c>
       <c r="G83">
-        <v>-2.176221366363642</v>
+        <v>-4.580505064259341</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-14.56540624965058</v>
       </c>
       <c r="E84">
-        <v>-18.9656316126477</v>
+        <v>-22.13568115834115</v>
       </c>
       <c r="F84">
-        <v>-0.5055328923583788</v>
+        <v>-0.6609255050821353</v>
       </c>
       <c r="G84">
-        <v>-1.67025082832359</v>
+        <v>-4.034682179017543</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-14.40807325954268</v>
       </c>
       <c r="E85">
-        <v>-19.39814163664629</v>
+        <v>-22.44699110399845</v>
       </c>
       <c r="F85">
-        <v>-0.6762039134593694</v>
+        <v>-1.169309490793442</v>
       </c>
       <c r="G85">
-        <v>-1.151395647044696</v>
+        <v>-4.14525771057474</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-14.23439894150326</v>
       </c>
       <c r="E86">
-        <v>-20.40944045203923</v>
+        <v>-23.37940390217778</v>
       </c>
       <c r="F86">
-        <v>-1.119199889863295</v>
+        <v>-1.120937804674368</v>
       </c>
       <c r="G86">
-        <v>-1.460514526228603</v>
+        <v>-4.002301733097932</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-14.0416417682902</v>
       </c>
       <c r="E87">
-        <v>-21.68529724743429</v>
+        <v>-24.53860720713524</v>
       </c>
       <c r="F87">
-        <v>-1.091000606737194</v>
+        <v>-1.338013139312784</v>
       </c>
       <c r="G87">
-        <v>-0.9576492799043888</v>
+        <v>-5.056998504817722</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-13.8266483848244</v>
       </c>
       <c r="E88">
-        <v>-22.27614536511107</v>
+        <v>-24.69666906389897</v>
       </c>
       <c r="F88">
-        <v>-1.521972001922081</v>
+        <v>-1.62961917428328</v>
       </c>
       <c r="G88">
-        <v>-1.199580637368788</v>
+        <v>-3.822121981577558</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-13.59592670617818</v>
       </c>
       <c r="E89">
-        <v>-24.08551526877179</v>
+        <v>-27.03982831273983</v>
       </c>
       <c r="F89">
-        <v>-1.595542624434317</v>
+        <v>-1.423148599135503</v>
       </c>
       <c r="G89">
-        <v>-0.8055926127401238</v>
+        <v>-3.971182605028783</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-13.34176185784244</v>
       </c>
       <c r="E90">
-        <v>-25.86034650117601</v>
+        <v>-28.33533415685416</v>
       </c>
       <c r="F90">
-        <v>-2.01621244259799</v>
+        <v>-1.650735087748042</v>
       </c>
       <c r="G90">
-        <v>-0.8959407110523738</v>
+        <v>-4.087091425449746</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-13.07978960500903</v>
       </c>
       <c r="E91">
-        <v>-28.24674361984211</v>
+        <v>-29.5780583721721</v>
       </c>
       <c r="F91">
-        <v>-2.25096016740773</v>
+        <v>-1.9460878284814</v>
       </c>
       <c r="G91">
-        <v>-0.7894338399629411</v>
+        <v>-3.312907108909021</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-12.80100979977578</v>
       </c>
       <c r="E92">
-        <v>-29.67423183891</v>
+        <v>-31.23183217316627</v>
       </c>
       <c r="F92">
-        <v>-2.494548229140147</v>
+        <v>-2.477372859410502</v>
       </c>
       <c r="G92">
-        <v>0.1438552951951562</v>
+        <v>-4.276014327739334</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-12.5295456576689</v>
       </c>
       <c r="E93">
-        <v>-30.82260529827812</v>
+        <v>-32.71693843127075</v>
       </c>
       <c r="F93">
-        <v>-2.598958970058608</v>
+        <v>-2.122792677744382</v>
       </c>
       <c r="G93">
-        <v>-0.6795766967877661</v>
+        <v>-4.039631444598753</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-12.26217888597604</v>
       </c>
       <c r="E94">
-        <v>-32.65390207308398</v>
+        <v>-34.78200635553758</v>
       </c>
       <c r="F94">
-        <v>-2.807497150243773</v>
+        <v>-2.389610646553506</v>
       </c>
       <c r="G94">
-        <v>-1.146012699997841</v>
+        <v>-3.890997881522095</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-12.02361306062506</v>
       </c>
       <c r="E95">
-        <v>-35.58919326198279</v>
+        <v>-36.60970525774434</v>
       </c>
       <c r="F95">
-        <v>-2.843227949796126</v>
+        <v>-2.770984371863176</v>
       </c>
       <c r="G95">
-        <v>-1.209254051434538</v>
+        <v>-3.943218426858559</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-11.8216014974816</v>
       </c>
       <c r="E96">
-        <v>-37.90271817691746</v>
+        <v>-38.83227124376094</v>
       </c>
       <c r="F96">
-        <v>-3.473042313083813</v>
+        <v>-3.077766926020362</v>
       </c>
       <c r="G96">
-        <v>-1.433328326260108</v>
+        <v>-4.718256864148415</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-11.66941030392078</v>
       </c>
       <c r="E97">
-        <v>-39.63290091984305</v>
+        <v>-40.82794936080823</v>
       </c>
       <c r="F97">
-        <v>-3.346756045792223</v>
+        <v>-3.214041647454908</v>
       </c>
       <c r="G97">
-        <v>-1.714092382900159</v>
+        <v>-4.113132176661653</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-11.58431977859451</v>
       </c>
       <c r="E98">
-        <v>-42.87988018197881</v>
+        <v>-42.53541727811135</v>
       </c>
       <c r="F98">
-        <v>-3.699804576130566</v>
+        <v>-3.793961785337175</v>
       </c>
       <c r="G98">
-        <v>-2.1172671714003</v>
+        <v>-4.497575898500598</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-11.55844085461827</v>
       </c>
       <c r="E99">
-        <v>-45.27348210279111</v>
+        <v>-45.45995786971596</v>
       </c>
       <c r="F99">
-        <v>-3.801981210163677</v>
+        <v>-3.813347239297489</v>
       </c>
       <c r="G99">
-        <v>-2.538219589446328</v>
+        <v>-5.394607938912597</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-11.6221780771592</v>
       </c>
       <c r="E100">
-        <v>-47.63999016361551</v>
+        <v>-47.71048265425591</v>
       </c>
       <c r="F100">
-        <v>-3.978454944921278</v>
+        <v>-4.070826194007451</v>
       </c>
       <c r="G100">
-        <v>-2.542685515378805</v>
+        <v>-5.478752074884253</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-11.73263995057851</v>
       </c>
       <c r="E101">
-        <v>-49.56423726378431</v>
+        <v>-49.38621502571328</v>
       </c>
       <c r="F101">
-        <v>-4.315128308441081</v>
+        <v>-4.179061507224637</v>
       </c>
       <c r="G101">
-        <v>-3.208691135332765</v>
+        <v>-5.515932811835808</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-11.95446072819158</v>
       </c>
       <c r="E102">
-        <v>-52.24262472587248</v>
+        <v>-52.34023598310782</v>
       </c>
       <c r="F102">
-        <v>-4.644845870879577</v>
+        <v>-4.133537748236388</v>
       </c>
       <c r="G102">
-        <v>-3.661530728013052</v>
+        <v>-6.255766907861054</v>
       </c>
     </row>
   </sheetData>
